--- a/results/job_matches_2026-05-31.xlsx
+++ b/results/job_matches_2026-05-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate Data Solutions Architect</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c665018c2e31d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a442a59c169c0e12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Developer / AI Focused</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61c6b86bc3293d8</t>
+          <t>https://www.indeed.com/viewjob?jk=37fb3c3c32f07e3a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Diality</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905414e7ceb13800</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ebbbc1d7b8af0a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a442a59c169c0e12</t>
+          <t>https://www.indeed.com/viewjob?jk=fb5357934afa21e5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fb3c3c32f07e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c4a730c4213f26</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb5357934afa21e5</t>
+          <t>https://www.indeed.com/viewjob?jk=496001bd37adfeff</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c4a730c4213f26</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a0a2abf135bec7</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496001bd37adfeff</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9fbbc3e7567428</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a0a2abf135bec7</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b2e92720439ad</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9fbbc3e7567428</t>
+          <t>https://www.indeed.com/viewjob?jk=59a5df775340e20b</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b2e92720439ad</t>
+          <t>https://www.indeed.com/viewjob?jk=480b651f50c6dea5</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a5df775340e20b</t>
+          <t>https://www.indeed.com/viewjob?jk=66dafa4abc2f61b9</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480b651f50c6dea5</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba4f65f74407a3b</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66dafa4abc2f61b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8ed2ef1db2cc04</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba4f65f74407a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=59b457d7ec7273da</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8ed2ef1db2cc04</t>
+          <t>https://www.indeed.com/viewjob?jk=70be489e957f5b4a</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b457d7ec7273da</t>
+          <t>https://www.indeed.com/viewjob?jk=60c4c1858004a062</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70be489e957f5b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=787345db7c153b6c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c4c1858004a062</t>
+          <t>https://www.indeed.com/viewjob?jk=95d82ec4ef0bd93e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787345db7c153b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb305cde26804c4c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d82ec4ef0bd93e</t>
+          <t>https://www.indeed.com/viewjob?jk=70637e3722460777</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb305cde26804c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=91ff1e313ad56961</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70637e3722460777</t>
+          <t>https://www.indeed.com/viewjob?jk=759cdb13aefadafc</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ff1e313ad56961</t>
+          <t>https://www.indeed.com/viewjob?jk=eece0009ff527849</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759cdb13aefadafc</t>
+          <t>https://www.indeed.com/viewjob?jk=350f47b8a167f9c0</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece0009ff527849</t>
+          <t>https://www.indeed.com/viewjob?jk=4b557c32e5ec4a4e</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350f47b8a167f9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c5c106834341be</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b557c32e5ec4a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=93f1e7dc6f24d543</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c5c106834341be</t>
+          <t>https://www.indeed.com/viewjob?jk=892900737aeac790</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f1e7dc6f24d543</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf2ceff8e884105</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892900737aeac790</t>
+          <t>https://www.indeed.com/viewjob?jk=009ae6b6d8f874a5</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf2ceff8e884105</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f860e0ba8d395b</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009ae6b6d8f874a5</t>
+          <t>https://www.indeed.com/viewjob?jk=78e66503bc5b2c76</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f860e0ba8d395b</t>
+          <t>https://www.indeed.com/viewjob?jk=76f1d0d445006fcd</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e66503bc5b2c76</t>
+          <t>https://www.indeed.com/viewjob?jk=165107ab6e6726fe</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76f1d0d445006fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=d8fa5dfcaac54a21</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=165107ab6e6726fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bce763a9bc77dcb0</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8fa5dfcaac54a21</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee36daa1faed1a5</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce763a9bc77dcb0</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdaa31bd60d4e9e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee36daa1faed1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3621a89722a9f88a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdaa31bd60d4e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=60e8fd5ad65f18ca</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3621a89722a9f88a</t>
+          <t>https://www.indeed.com/viewjob?jk=5139116177d9549b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e8fd5ad65f18ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c3488847e537d4d5</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5139116177d9549b</t>
+          <t>https://www.indeed.com/viewjob?jk=1de8d03cbe1378f4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3488847e537d4d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7f609f3a296bdab7</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de8d03cbe1378f4</t>
+          <t>https://www.indeed.com/viewjob?jk=81ac97b136c5456f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f609f3a296bdab7</t>
+          <t>https://www.indeed.com/viewjob?jk=9123d16dd1cc18df</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ac97b136c5456f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8d13fd70eda4d5f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9123d16dd1cc18df</t>
+          <t>https://www.indeed.com/viewjob?jk=453caa8d182425c0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d13fd70eda4d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=54a9ea00dd6179e4</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=453caa8d182425c0</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae464dc92c71bb9</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a9ea00dd6179e4</t>
+          <t>https://www.indeed.com/viewjob?jk=995348093b9d831f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae464dc92c71bb9</t>
+          <t>https://www.indeed.com/viewjob?jk=29e8bff1e2c02deb</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995348093b9d831f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5446af907994aa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e8bff1e2c02deb</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5446af907994aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f006fa81cdf81471</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,24 +2446,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=b8181bbf8bb6bc15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f006fa81cdf81471</t>
+          <t>https://www.indeed.com/viewjob?jk=c767a8767951e5ec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8181bbf8bb6bc15</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb069ac36084d84</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2561,129 +2561,129 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c767a8767951e5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=65c7a1de08aa3bbd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb069ac36084d84</t>
+          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer Remote - w2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>itheroes inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c7a1de08aa3bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Analytics Engineering</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad61eb5cd2a5633</t>
+          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
+          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
+          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
+          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
+          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
+          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
+          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
+          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
+          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,42 +3811,42 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb50dd6047fba4fd</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
+          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,215 +3891,40 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
+          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb50dd6047fba4fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>DevOps Engineer - Mid</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Nalley Consulting</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35023775c057de52</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Shared Services</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>HeroDevs</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6847e3d78dab687e</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
         </is>

--- a/results/job_matches_2026-05-31.xlsx
+++ b/results/job_matches_2026-05-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
+          <t>Sr. SaaS Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Peloton</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb5357934afa21e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4058b3adc556b797</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c4a730c4213f26</t>
+          <t>https://www.indeed.com/viewjob?jk=fb5357934afa21e5</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496001bd37adfeff</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c4a730c4213f26</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a0a2abf135bec7</t>
+          <t>https://www.indeed.com/viewjob?jk=496001bd37adfeff</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9fbbc3e7567428</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a0a2abf135bec7</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b2e92720439ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9fbbc3e7567428</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a5df775340e20b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b2e92720439ad</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480b651f50c6dea5</t>
+          <t>https://www.indeed.com/viewjob?jk=59a5df775340e20b</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66dafa4abc2f61b9</t>
+          <t>https://www.indeed.com/viewjob?jk=480b651f50c6dea5</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba4f65f74407a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=66dafa4abc2f61b9</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8ed2ef1db2cc04</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba4f65f74407a3b</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b457d7ec7273da</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8ed2ef1db2cc04</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70be489e957f5b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=59b457d7ec7273da</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c4c1858004a062</t>
+          <t>https://www.indeed.com/viewjob?jk=70be489e957f5b4a</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787345db7c153b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=60c4c1858004a062</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d82ec4ef0bd93e</t>
+          <t>https://www.indeed.com/viewjob?jk=787345db7c153b6c</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb305cde26804c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=95d82ec4ef0bd93e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70637e3722460777</t>
+          <t>https://www.indeed.com/viewjob?jk=cb305cde26804c4c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ff1e313ad56961</t>
+          <t>https://www.indeed.com/viewjob?jk=70637e3722460777</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759cdb13aefadafc</t>
+          <t>https://www.indeed.com/viewjob?jk=91ff1e313ad56961</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece0009ff527849</t>
+          <t>https://www.indeed.com/viewjob?jk=759cdb13aefadafc</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350f47b8a167f9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=eece0009ff527849</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b557c32e5ec4a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=350f47b8a167f9c0</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c5c106834341be</t>
+          <t>https://www.indeed.com/viewjob?jk=4b557c32e5ec4a4e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f1e7dc6f24d543</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c5c106834341be</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892900737aeac790</t>
+          <t>https://www.indeed.com/viewjob?jk=93f1e7dc6f24d543</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf2ceff8e884105</t>
+          <t>https://www.indeed.com/viewjob?jk=892900737aeac790</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009ae6b6d8f874a5</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf2ceff8e884105</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f860e0ba8d395b</t>
+          <t>https://www.indeed.com/viewjob?jk=009ae6b6d8f874a5</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e66503bc5b2c76</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f860e0ba8d395b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76f1d0d445006fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=78e66503bc5b2c76</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=165107ab6e6726fe</t>
+          <t>https://www.indeed.com/viewjob?jk=76f1d0d445006fcd</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8fa5dfcaac54a21</t>
+          <t>https://www.indeed.com/viewjob?jk=165107ab6e6726fe</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce763a9bc77dcb0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8fa5dfcaac54a21</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee36daa1faed1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bce763a9bc77dcb0</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdaa31bd60d4e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee36daa1faed1a5</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3621a89722a9f88a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdaa31bd60d4e9e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e8fd5ad65f18ca</t>
+          <t>https://www.indeed.com/viewjob?jk=3621a89722a9f88a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5139116177d9549b</t>
+          <t>https://www.indeed.com/viewjob?jk=60e8fd5ad65f18ca</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3488847e537d4d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5139116177d9549b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de8d03cbe1378f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c3488847e537d4d5</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f609f3a296bdab7</t>
+          <t>https://www.indeed.com/viewjob?jk=1de8d03cbe1378f4</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ac97b136c5456f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f609f3a296bdab7</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9123d16dd1cc18df</t>
+          <t>https://www.indeed.com/viewjob?jk=81ac97b136c5456f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d13fd70eda4d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=9123d16dd1cc18df</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=453caa8d182425c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f8d13fd70eda4d5f</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a9ea00dd6179e4</t>
+          <t>https://www.indeed.com/viewjob?jk=453caa8d182425c0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae464dc92c71bb9</t>
+          <t>https://www.indeed.com/viewjob?jk=54a9ea00dd6179e4</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995348093b9d831f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae464dc92c71bb9</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e8bff1e2c02deb</t>
+          <t>https://www.indeed.com/viewjob?jk=995348093b9d831f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5446af907994aa</t>
+          <t>https://www.indeed.com/viewjob?jk=29e8bff1e2c02deb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5446af907994aa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f006fa81cdf81471</t>
+          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8181bbf8bb6bc15</t>
+          <t>https://www.indeed.com/viewjob?jk=f006fa81cdf81471</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c767a8767951e5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b8181bbf8bb6bc15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb069ac36084d84</t>
+          <t>https://www.indeed.com/viewjob?jk=c767a8767951e5ec</t>
         </is>
       </c>
     </row>
@@ -2561,207 +2561,207 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c7a1de08aa3bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb069ac36084d84</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
+          <t>https://www.indeed.com/viewjob?jk=65c7a1de08aa3bbd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e08e23d0eaf7fd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=cc30e0ac9bbb52ca</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>Redshift, S3, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=f50dd3b28c07a04c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
+          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Data Engineer Remote - w2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>itheroes inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
+          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
+          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
+          <t>https://www.indeed.com/viewjob?jk=405b65a4422a7305</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
+          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
+          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
+          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
+          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
+          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
+          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
+          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
+          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,42 +3811,42 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb50dd6047fba4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53279f54b14e6849</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,42 +3891,392 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a92d266fe841f72</t>
+          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>Software Engineer II- Full-stack Developer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Engineer II- Full-stack Developer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Engineer II- Full-stack Developer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer II- Full-stack Developer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Cloud Engineering</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Axon</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5b1a6d36f2381e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Search Relevance</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Box</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Applications Engineer, Full Stack - People</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Wellhub</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Developer Advocate - Data Observability</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Datadog, Python</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24166b9fe873f35e</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D109" t="n">
         <v>10.4</v>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Hawthorne, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae57e531c0d4208e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-31.xlsx
+++ b/results/job_matches_2026-05-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836bfed93aa23557</t>
+          <t>https://www.indeed.com/viewjob?jk=f006fa81cdf81471</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f006fa81cdf81471</t>
+          <t>https://www.indeed.com/viewjob?jk=b8181bbf8bb6bc15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8181bbf8bb6bc15</t>
+          <t>https://www.indeed.com/viewjob?jk=c767a8767951e5ec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c767a8767951e5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb069ac36084d84</t>
         </is>
       </c>
     </row>
@@ -2561,49 +2561,49 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb069ac36084d84</t>
+          <t>https://www.indeed.com/viewjob?jk=65c7a1de08aa3bbd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c7a1de08aa3bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e08e23d0eaf7fd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e08e23d0eaf7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=cc30e0ac9bbb52ca</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, S3, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc30e0ac9bbb52ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f50dd3b28c07a04c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,69 +2691,69 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50dd3b28c07a04c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Data Engineer Remote - w2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>itheroes inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
+          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,129 +2771,129 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0487f884b026bec9</t>
+          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
+          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=405b65a4422a7305</t>
+          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer IV</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
+          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
+          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
+          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
+          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
+          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
+          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
+          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
+          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,129 +3926,129 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Senior Software Engineer, Search Relevance</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
+          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wellhub</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer II, Cloud Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b1a6d36f2381e4</t>
+          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Search Relevance</t>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,190 +4091,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Applications Engineer, Full Stack - People</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Wellhub</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Developer Advocate - Data Observability</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Datadog, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24166b9fe873f35e</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Hawthorne, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae57e531c0d4208e</t>
         </is>

--- a/results/job_matches_2026-05-31.xlsx
+++ b/results/job_matches_2026-05-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2743,87 +2743,87 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab00f608359b4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
+          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
+          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer IV</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
+          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
+          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
+          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
+          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
+          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
+          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,59 +3891,59 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
+          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Senior Software Engineer, Search Relevance</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
+          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Search Relevance</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
+          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Wellhub</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,29 +3986,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wellhub</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
+          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,50 +4056,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Hawthorne, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae57e531c0d4208e</t>
         </is>

--- a/results/job_matches_2026-05-31.xlsx
+++ b/results/job_matches_2026-05-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>MS Server/Networking</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f006fa81cdf81471</t>
+          <t>https://www.indeed.com/viewjob?jk=29bfb74f7babb87c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8181bbf8bb6bc15</t>
+          <t>https://www.indeed.com/viewjob?jk=f006fa81cdf81471</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c767a8767951e5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b8181bbf8bb6bc15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb069ac36084d84</t>
+          <t>https://www.indeed.com/viewjob?jk=c767a8767951e5ec</t>
         </is>
       </c>
     </row>
@@ -2561,49 +2561,49 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c7a1de08aa3bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb069ac36084d84</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e08e23d0eaf7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=65c7a1de08aa3bbd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc30e0ac9bbb52ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e08e23d0eaf7fd</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,139 +2691,139 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
+          <t>https://www.indeed.com/viewjob?jk=cc30e0ac9bbb52ca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
+          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>Data Engineer Remote - w2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>itheroes inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
+          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
+          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer IV</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
+          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
+          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
+          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
+          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
+          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
+          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
+          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,59 +3891,59 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Search Relevance</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
+          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Senior Software Engineer, Search Relevance</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
+          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Wellhub</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,29 +3986,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Wellhub</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hawthorne, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,15 +4056,50 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Hawthorne, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae57e531c0d4208e</t>
         </is>

--- a/results/job_matches_2026-05-31.xlsx
+++ b/results/job_matches_2026-05-31.xlsx
@@ -2638,7 +2638,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50dd3b28c07a04c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc30e0ac9bbb52ca</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, S3, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc30e0ac9bbb52ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f50dd3b28c07a04c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-31.xlsx
+++ b/results/job_matches_2026-05-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50dd3b28c07a04c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e1fdd788472d792</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,139 +2726,139 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>Redshift, S3, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
+          <t>https://www.indeed.com/viewjob?jk=f50dd3b28c07a04c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
+          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>Data Engineer Remote - w2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>itheroes inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
+          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
+          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer IV</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
+          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
+          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
+          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
+          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
+          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
+          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
+          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,59 +3926,59 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Search Relevance</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
+          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Senior Software Engineer, Search Relevance</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
+          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wellhub</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,29 +4021,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Wellhub</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hawthorne, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,15 +4091,50 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Hawthorne, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae57e531c0d4208e</t>
         </is>

--- a/results/job_matches_2026-05-31.xlsx
+++ b/results/job_matches_2026-05-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a442a59c169c0e12</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ebbbc1d7b8af0a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Sr. SaaS Solutions Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Peloton</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fb3c3c32f07e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=4058b3adc556b797</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebbbc1d7b8af0a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb5357934afa21e5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. SaaS Solutions Architect</t>
+          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Peloton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4058b3adc556b797</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c4a730c4213f26</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb5357934afa21e5</t>
+          <t>https://www.indeed.com/viewjob?jk=496001bd37adfeff</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c4a730c4213f26</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a0a2abf135bec7</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496001bd37adfeff</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9fbbc3e7567428</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a0a2abf135bec7</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8b2e92720439ad</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9fbbc3e7567428</t>
+          <t>https://www.indeed.com/viewjob?jk=59a5df775340e20b</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b2e92720439ad</t>
+          <t>https://www.indeed.com/viewjob?jk=480b651f50c6dea5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a5df775340e20b</t>
+          <t>https://www.indeed.com/viewjob?jk=66dafa4abc2f61b9</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480b651f50c6dea5</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba4f65f74407a3b</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66dafa4abc2f61b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8ed2ef1db2cc04</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba4f65f74407a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=59b457d7ec7273da</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8ed2ef1db2cc04</t>
+          <t>https://www.indeed.com/viewjob?jk=70be489e957f5b4a</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b457d7ec7273da</t>
+          <t>https://www.indeed.com/viewjob?jk=60c4c1858004a062</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70be489e957f5b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=787345db7c153b6c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c4c1858004a062</t>
+          <t>https://www.indeed.com/viewjob?jk=95d82ec4ef0bd93e</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787345db7c153b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb305cde26804c4c</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d82ec4ef0bd93e</t>
+          <t>https://www.indeed.com/viewjob?jk=70637e3722460777</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb305cde26804c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=91ff1e313ad56961</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70637e3722460777</t>
+          <t>https://www.indeed.com/viewjob?jk=759cdb13aefadafc</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ff1e313ad56961</t>
+          <t>https://www.indeed.com/viewjob?jk=eece0009ff527849</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759cdb13aefadafc</t>
+          <t>https://www.indeed.com/viewjob?jk=350f47b8a167f9c0</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece0009ff527849</t>
+          <t>https://www.indeed.com/viewjob?jk=4b557c32e5ec4a4e</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350f47b8a167f9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c5c106834341be</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b557c32e5ec4a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=93f1e7dc6f24d543</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c5c106834341be</t>
+          <t>https://www.indeed.com/viewjob?jk=892900737aeac790</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f1e7dc6f24d543</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf2ceff8e884105</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892900737aeac790</t>
+          <t>https://www.indeed.com/viewjob?jk=009ae6b6d8f874a5</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf2ceff8e884105</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f860e0ba8d395b</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009ae6b6d8f874a5</t>
+          <t>https://www.indeed.com/viewjob?jk=78e66503bc5b2c76</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f860e0ba8d395b</t>
+          <t>https://www.indeed.com/viewjob?jk=76f1d0d445006fcd</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e66503bc5b2c76</t>
+          <t>https://www.indeed.com/viewjob?jk=165107ab6e6726fe</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76f1d0d445006fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=d8fa5dfcaac54a21</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=165107ab6e6726fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bce763a9bc77dcb0</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8fa5dfcaac54a21</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee36daa1faed1a5</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce763a9bc77dcb0</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdaa31bd60d4e9e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee36daa1faed1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3621a89722a9f88a</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdaa31bd60d4e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=60e8fd5ad65f18ca</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3621a89722a9f88a</t>
+          <t>https://www.indeed.com/viewjob?jk=5139116177d9549b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e8fd5ad65f18ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c3488847e537d4d5</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5139116177d9549b</t>
+          <t>https://www.indeed.com/viewjob?jk=1de8d03cbe1378f4</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3488847e537d4d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7f609f3a296bdab7</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de8d03cbe1378f4</t>
+          <t>https://www.indeed.com/viewjob?jk=81ac97b136c5456f</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f609f3a296bdab7</t>
+          <t>https://www.indeed.com/viewjob?jk=9123d16dd1cc18df</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ac97b136c5456f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8d13fd70eda4d5f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9123d16dd1cc18df</t>
+          <t>https://www.indeed.com/viewjob?jk=453caa8d182425c0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d13fd70eda4d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=54a9ea00dd6179e4</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=453caa8d182425c0</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae464dc92c71bb9</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a9ea00dd6179e4</t>
+          <t>https://www.indeed.com/viewjob?jk=995348093b9d831f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae464dc92c71bb9</t>
+          <t>https://www.indeed.com/viewjob?jk=29e8bff1e2c02deb</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,94 +2316,94 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995348093b9d831f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5446af907994aa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
+          <t>MS Server/Networking</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e8bff1e2c02deb</t>
+          <t>https://www.indeed.com/viewjob?jk=29bfb74f7babb87c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5446af907994aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f006fa81cdf81471</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MS Server/Networking</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bfb74f7babb87c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8181bbf8bb6bc15</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f006fa81cdf81471</t>
+          <t>https://www.indeed.com/viewjob?jk=c767a8767951e5ec</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8181bbf8bb6bc15</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb069ac36084d84</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,84 +2526,84 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c767a8767951e5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=65c7a1de08aa3bbd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb069ac36084d84</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e08e23d0eaf7fd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c7a1de08aa3bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=cc30e0ac9bbb52ca</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, S3, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e08e23d0eaf7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f50dd3b28c07a04c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,209 +2656,209 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc30e0ac9bbb52ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer Remote - w2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>itheroes inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1fdd788472d792</t>
+          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50dd3b28c07a04c</t>
+          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e53268b3ba5dc79</t>
+          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
+          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
+          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer IV</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
+          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
+          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
+          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
+          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
+          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
+          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
+          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
+          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,129 +3856,129 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Senior Software Engineer, Search Relevance</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
+          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wellhub</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Search Relevance</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
+          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,120 +4021,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Wellhub</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Hawthorne, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae57e531c0d4208e</t>
         </is>

--- a/results/job_matches_2026-05-31.xlsx
+++ b/results/job_matches_2026-05-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2673,87 +2673,87 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ba56caa4808317</t>
+          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
+          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d0db18285637cf</t>
+          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer IV</t>
+          <t>Software Engineer II- Full-stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecee2c31a53dd8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed9b32824038ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864981dbb6ec1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b9675ddf8e40e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a2f848f675e6acb</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b7dd0b8926d23</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae4ee5f3e14a81e</t>
+          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15998701a395b79</t>
+          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c695018ac7cacbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530fd646c6a074ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4c6dfd9006c76b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6b7dac9013891e</t>
+          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925bafcc9db4e0ff</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5bd61a49f1b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e58ee0df76cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f25ecdb1b681184</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e054cf46442c27</t>
+          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7659be2bedc23cb</t>
+          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81860298610f695e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb084a451f9c2849</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5c7553f00001ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc95576b7871ad1b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed059d654e490ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa061d87a21a8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c7df43c34f6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78fc022411bfcbc</t>
+          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019f5b9c90f9edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5642653865589c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,59 +3821,59 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ccba2cde0b6a448</t>
+          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II- Full-stack Developer</t>
+          <t>Senior Software Engineer, Search Relevance</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b83d9c17af70e6</t>
+          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Search Relevance</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
+          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Wellhub</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,29 +3916,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Wellhub</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
+          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,50 +3986,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=beee8870674f94b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Hawthorne, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae57e531c0d4208e</t>
         </is>
